--- a/artfynd/A 51825-2025 artfynd.xlsx
+++ b/artfynd/A 51825-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -867,6 +867,107 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129797589</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92893</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ormberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>540087</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6682643</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51825-2025 artfynd.xlsx
+++ b/artfynd/A 51825-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>129797589</v>
       </c>
       <c r="B4" t="n">
-        <v>92893</v>
+        <v>92897</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 51825-2025 artfynd.xlsx
+++ b/artfynd/A 51825-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>129797589</v>
       </c>
       <c r="B4" t="n">
-        <v>92897</v>
+        <v>92899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 51825-2025 artfynd.xlsx
+++ b/artfynd/A 51825-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>129797589</v>
       </c>
       <c r="B4" t="n">
-        <v>92899</v>
+        <v>92902</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 51825-2025 artfynd.xlsx
+++ b/artfynd/A 51825-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>129797589</v>
       </c>
       <c r="B4" t="n">
-        <v>92902</v>
+        <v>92905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 51825-2025 artfynd.xlsx
+++ b/artfynd/A 51825-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>129797589</v>
       </c>
       <c r="B4" t="n">
-        <v>92905</v>
+        <v>92906</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 51825-2025 artfynd.xlsx
+++ b/artfynd/A 51825-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128164820</v>
       </c>
       <c r="B2" t="n">
-        <v>91010</v>
+        <v>91166</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129797589</v>
       </c>
       <c r="B4" t="n">
-        <v>92906</v>
+        <v>92923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 51825-2025 artfynd.xlsx
+++ b/artfynd/A 51825-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128164820</v>
       </c>
       <c r="B2" t="n">
-        <v>91182</v>
+        <v>91184</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129797589</v>
       </c>
       <c r="B4" t="n">
-        <v>92939</v>
+        <v>92941</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 51825-2025 artfynd.xlsx
+++ b/artfynd/A 51825-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128164820</v>
       </c>
       <c r="B2" t="n">
-        <v>91184</v>
+        <v>91271</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51825-2025 artfynd.xlsx
+++ b/artfynd/A 51825-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128164820</v>
       </c>
       <c r="B2" t="n">
-        <v>91271</v>
+        <v>91274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51825-2025 artfynd.xlsx
+++ b/artfynd/A 51825-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128164820</v>
+        <v>128165248</v>
       </c>
       <c r="B2" t="n">
-        <v>91274</v>
+        <v>96338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5754</v>
+        <v>2809</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540074</v>
+        <v>540100</v>
       </c>
       <c r="R2" t="n">
-        <v>6682622</v>
+        <v>6682513</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,45 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128165248</v>
+        <v>129797589</v>
       </c>
       <c r="B3" t="n">
-        <v>95818</v>
+        <v>93215</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2809</v>
+        <v>4368</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ormberget, Ormberget, Dlr</t>
+          <t>Ormberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540100</v>
+        <v>540087</v>
       </c>
       <c r="R3" t="n">
-        <v>6682513</v>
+        <v>6682643</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -851,6 +854,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -869,10 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129797589</v>
+        <v>128164820</v>
       </c>
       <c r="B4" t="n">
-        <v>92941</v>
+        <v>91443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,37 +884,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4368</v>
+        <v>5754</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ormberget, Dlr</t>
+          <t>Ormberget, Ormberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540087</v>
+        <v>540074</v>
       </c>
       <c r="R4" t="n">
-        <v>6682643</v>
+        <v>6682622</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -951,7 +952,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -967,6 +967,129 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>88370729</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nisshyttan Säter, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>540106</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6682716</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-10-05</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-10-05</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lena Stigsdotter</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lena Stigsdotter</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51825-2025 artfynd.xlsx
+++ b/artfynd/A 51825-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165248</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129797589</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128164820</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,8 +1110,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88370729</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>